--- a/docs/Table.xlsx
+++ b/docs/Table.xlsx
@@ -56,13 +56,16 @@
     <style:style style:name="ce1" style:family="table-cell" style:parent-style-name="Default">
       <style:text-properties style:font-name="Times New Roman" fo:font-size="16pt"/>
     </style:style>
+    <style:style style:name="ce2" style:family="table-cell" style:parent-style-name="Default">
+      <style:text-properties style:font-name="Times New Roman" fo:font-size="16pt"/>
+    </style:style>
   </office:automatic-styles>
   <office:body>
     <office:spreadsheet>
       <table:calculation-settings table:automatic-find-labels="false" table:use-regular-expressions="false" table:use-wildcards="true" table:null-year="1950"/>
       <table:table table:name="Лист1" table:style-name="ta1">
-        <table:table-column table:style-name="co1" table:default-cell-style-name="ce1"/>
-        <table:table-column table:style-name="co2" table:default-cell-style-name="ce1"/>
+        <table:table-column table:style-name="co1" table:default-cell-style-name="ce2"/>
+        <table:table-column table:style-name="co2" table:default-cell-style-name="ce2"/>
         <table:table-row table:style-name="ro1">
           <table:table-cell office:value-type="string" calcext:value-type="string">
             <text:p>КОГДА</text:p>
@@ -15468,12 +15471,12 @@
           <config:config-item-map-named config:name="Tables">
             <config:config-item-map-entry config:name="Лист1">
               <config:config-item config:name="CursorPositionX" config:type="int">1</config:config-item>
-              <config:config-item config:name="CursorPositionY" config:type="int">1800</config:config-item>
+              <config:config-item config:name="CursorPositionY" config:type="int">1825</config:config-item>
               <config:config-item config:name="ActiveSplitRange" config:type="short">2</config:config-item>
               <config:config-item config:name="PositionLeft" config:type="int">0</config:config-item>
               <config:config-item config:name="PositionRight" config:type="int">0</config:config-item>
               <config:config-item config:name="PositionTop" config:type="int">0</config:config-item>
-              <config:config-item config:name="PositionBottom" config:type="int">1794</config:config-item>
+              <config:config-item config:name="PositionBottom" config:type="int">1814</config:config-item>
               <config:config-item config:name="ZoomType" config:type="short">0</config:config-item>
               <config:config-item config:name="ZoomValue" config:type="int">95</config:config-item>
               <config:config-item config:name="PageViewZoomValue" config:type="int">60</config:config-item>
@@ -15542,7 +15545,7 @@
       <config:config-item config:name="LoadReadonly" config:type="boolean">false</config:config-item>
       <config:config-item config:name="PrinterName" config:type="string">Generic Printer</config:config-item>
       <config:config-item config:name="PrinterPaperFromSetup" config:type="boolean">false</config:config-item>
-      <config:config-item config:name="PrinterSetup" config:type="base64Binary">wAH+/0dlbmVyaWMgUHJpbnRlcgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAU0dFTlBSVAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAWAAMArAAAAAAAAAAEAAhSAAAEdAAASm9iRGF0YSAxCnByaW50ZXI9R2VuZXJpYyBQcmludGVyCm9yaWVudGF0aW9uPVBvcnRyYWl0CmNvcGllcz0xCmNvbGxhdGU9ZmFsc2UKbWFyZ2luYWRqdXN0bWVudD0wLDAsJzAsMApjb2xvcmRlcHRoPTI0CmNvbG9yZGV2aWNlPTAKUFBEQ29udGV4dERhdGEKRHVwbGV4Ok5vbmUAUGFnZVNpemU6QTQAABIAQ09NUEFUX0RVUExFWF9NT0RFDwBEdXBsZXhNb2RlOjpPZmYMAFBSSU5URVJfTkFNRQ8AR2VuZXJpYyBQcmludGVyCwBEUklWRVJfTkFNRQcAU0dFTlBSVA==</config:config-item>
+      <config:config-item config:name="PrinterSetup" config:type="base64Binary">wAH+/0dlbmVyaWMgUHJpbnRlcgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAU0dFTlBSVAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAWAAMArAAAAAAAAAAEAAhSAAAEdAAASm9iRGF0YSAxCnByaW50ZXI9R2VuZXJpYyBQcmludGVyCm9yaWVudGF0aW9uPVBvcnRyYWl0CmNvcGllcz0xCmNvbGxhdGU9ZmFsc2UKbWFyZ2luYWRqdXN0bWVudD0wLDAsJzAsMApjb2xvcmRlcHRoPTI0CmNvbG9yZGV2aWNlPTAKUFBEQ29udGV4dERhdGEKUGFnZVNpemU6QTQARHVwbGV4Ok5vbmUAABIAQ09NUEFUX0RVUExFWF9NT0RFDwBEdXBsZXhNb2RlOjpPZmYMAFBSSU5URVJfTkFNRQ8AR2VuZXJpYyBQcmludGVyCwBEUklWRVJfTkFNRQcAU0dFTlBSVA==</config:config-item>
       <config:config-item config:name="RasterIsVisible" config:type="boolean">false</config:config-item>
       <config:config-item config:name="RasterResolutionX" config:type="int">1000</config:config-item>
       <config:config-item config:name="RasterResolutionY" config:type="int">1000</config:config-item>
@@ -15743,9 +15746,9 @@
         </style:region-left>
         <style:region-right>
           <text:p>
-            <text:date style:data-style-name="N2" text:date-value="2026-09-06">00.00.0000</text:date>
+            <text:date style:data-style-name="N2" text:date-value="2026-09-22">00.00.0000</text:date>
             , 
-            <text:time style:data-style-name="N2" text:time-value="12:17:50.268477043">00:00:00</text:time>
+            <text:time style:data-style-name="N2" text:time-value="18:51:25.428047938">00:00:00</text:time>
           </text:p>
         </style:region-right>
       </style:header>
